--- a/1_Sessions/B2_Ham_va_KPI/Demo/B2_Demo_Lookup.xlsx
+++ b/1_Sessions/B2_Ham_va_KPI/Demo/B2_Demo_Lookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6366da15f1f739f9/MCI Excel/1_Sessions/B2_Ham_va_KPI/Demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_6AFB75794664D8E4BA6F649A3D1F34AF9481B0BD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_6AFB75794664D8E4BA6F649A3D1F34AF9481B0BD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{022F591B-8CC3-4059-8FCA-526D43FD0310}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="Demo_KieuKhoa" sheetId="5" r:id="rId5"/>
     <sheet name="Huong_dan" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Demo_KhoaTrung!$A$8:$F$151</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1321,7 +1324,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
@@ -1329,7 +1332,7 @@
     <col min="4" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1346,7 +1349,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -1363,7 +1366,7 @@
         <v>23000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -1380,7 +1383,7 @@
         <v>43000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -1397,7 +1400,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1414,7 +1417,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1431,7 +1434,7 @@
         <v>83500</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -1448,7 +1451,7 @@
         <v>31500</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -1465,7 +1468,7 @@
         <v>283000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
@@ -1482,7 +1485,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
@@ -1499,7 +1502,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
@@ -1516,7 +1519,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -1533,7 +1536,7 @@
         <v>388000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>39</v>
       </c>
@@ -1550,7 +1553,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -1567,7 +1570,7 @@
         <v>102500</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>43</v>
       </c>
@@ -1584,7 +1587,7 @@
         <v>119000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
@@ -1601,7 +1604,7 @@
         <v>41500</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
@@ -1618,7 +1621,7 @@
         <v>26500</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>49</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>22500</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>51</v>
       </c>
@@ -1652,7 +1655,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>53</v>
       </c>
@@ -1669,7 +1672,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>55</v>
       </c>
@@ -1686,7 +1689,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>57</v>
       </c>
@@ -1703,7 +1706,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>57</v>
       </c>
@@ -1720,7 +1723,7 @@
         <v>69000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>61</v>
       </c>
@@ -1737,7 +1740,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>63</v>
       </c>
@@ -1754,7 +1757,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>65</v>
       </c>
@@ -1771,7 +1774,7 @@
         <v>52500</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>67</v>
       </c>
@@ -1788,7 +1791,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>69</v>
       </c>
@@ -1805,7 +1808,7 @@
         <v>11500</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
@@ -1822,7 +1825,7 @@
         <v>390000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>72</v>
       </c>
@@ -1839,7 +1842,7 @@
         <v>102500</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>75</v>
       </c>
@@ -1856,7 +1859,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>77</v>
       </c>
@@ -1873,7 +1876,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>79</v>
       </c>
@@ -1890,7 +1893,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>81</v>
       </c>
@@ -1907,7 +1910,7 @@
         <v>39000</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>83</v>
       </c>
@@ -1924,7 +1927,7 @@
         <v>37000</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>85</v>
       </c>
@@ -1941,7 +1944,7 @@
         <v>118500</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>88</v>
       </c>
@@ -1958,7 +1961,7 @@
         <v>22500</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>90</v>
       </c>
@@ -1975,7 +1978,7 @@
         <v>30500</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>92</v>
       </c>
@@ -1992,7 +1995,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>94</v>
       </c>
@@ -2009,7 +2012,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
@@ -2026,7 +2029,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>97</v>
       </c>
@@ -2051,14 +2054,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2072,7 +2075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -2086,7 +2089,7 @@
       </c>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2100,7 +2103,7 @@
       </c>
       <c r="D3" s="5"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2114,7 +2117,7 @@
       </c>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2130,7 +2133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -2146,7 +2149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -2168,7 +2171,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2178,7 +2181,7 @@
     <col min="6" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2196,7 +2199,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -2216,7 +2219,7 @@
         <v>P014</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2236,7 +2239,7 @@
         <v>P039</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2256,7 +2259,7 @@
         <v>P027</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2269,7 +2272,7 @@
         <v>Không có mã</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -2282,7 +2285,7 @@
         <v>Không có mã</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -2303,7 +2306,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F151"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -2313,12 +2316,12 @@
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>104</v>
       </c>
@@ -2327,7 +2330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>105</v>
       </c>
@@ -2336,7 +2339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>106</v>
       </c>
@@ -2345,7 +2348,7 @@
         <v>15872000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>107</v>
       </c>
@@ -2354,7 +2357,7 @@
         <v>17664000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>108</v>
       </c>
@@ -2374,7 +2377,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>113</v>
       </c>
@@ -2396,7 +2399,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>114</v>
       </c>
@@ -2418,7 +2421,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>115</v>
       </c>
@@ -2440,7 +2443,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>116</v>
       </c>
@@ -2462,7 +2465,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>117</v>
       </c>
@@ -2484,7 +2487,7 @@
         <v>372000</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>118</v>
       </c>
@@ -2506,7 +2509,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>119</v>
       </c>
@@ -2528,7 +2531,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>120</v>
       </c>
@@ -2550,7 +2553,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>121</v>
       </c>
@@ -2572,7 +2575,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>122</v>
       </c>
@@ -2594,7 +2597,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>123</v>
       </c>
@@ -2616,7 +2619,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>124</v>
       </c>
@@ -2638,7 +2641,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>125</v>
       </c>
@@ -2660,7 +2663,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>126</v>
       </c>
@@ -2682,7 +2685,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>127</v>
       </c>
@@ -2704,7 +2707,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>128</v>
       </c>
@@ -2726,7 +2729,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>129</v>
       </c>
@@ -2748,7 +2751,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>130</v>
       </c>
@@ -2770,7 +2773,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>131</v>
       </c>
@@ -2792,7 +2795,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>132</v>
       </c>
@@ -2814,7 +2817,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>133</v>
       </c>
@@ -2836,7 +2839,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>134</v>
       </c>
@@ -2858,7 +2861,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>135</v>
       </c>
@@ -2880,7 +2883,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>136</v>
       </c>
@@ -2902,7 +2905,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>137</v>
       </c>
@@ -2924,7 +2927,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>138</v>
       </c>
@@ -2946,7 +2949,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>139</v>
       </c>
@@ -2968,7 +2971,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>140</v>
       </c>
@@ -2990,7 +2993,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>141</v>
       </c>
@@ -3012,7 +3015,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>142</v>
       </c>
@@ -3034,7 +3037,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>143</v>
       </c>
@@ -3056,7 +3059,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>144</v>
       </c>
@@ -3078,7 +3081,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>145</v>
       </c>
@@ -3100,7 +3103,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>146</v>
       </c>
@@ -3122,7 +3125,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>147</v>
       </c>
@@ -3144,7 +3147,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>148</v>
       </c>
@@ -3166,7 +3169,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>149</v>
       </c>
@@ -3188,7 +3191,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>150</v>
       </c>
@@ -3210,7 +3213,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>151</v>
       </c>
@@ -3232,7 +3235,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>152</v>
       </c>
@@ -3254,7 +3257,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>153</v>
       </c>
@@ -3276,7 +3279,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>154</v>
       </c>
@@ -3298,7 +3301,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>155</v>
       </c>
@@ -3320,7 +3323,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>156</v>
       </c>
@@ -3342,7 +3345,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>157</v>
       </c>
@@ -3364,7 +3367,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>158</v>
       </c>
@@ -3386,7 +3389,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>159</v>
       </c>
@@ -3408,7 +3411,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>160</v>
       </c>
@@ -3430,7 +3433,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>161</v>
       </c>
@@ -3452,7 +3455,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>162</v>
       </c>
@@ -3474,7 +3477,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>163</v>
       </c>
@@ -3496,7 +3499,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>164</v>
       </c>
@@ -3518,7 +3521,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>165</v>
       </c>
@@ -3540,7 +3543,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>166</v>
       </c>
@@ -3562,7 +3565,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>167</v>
       </c>
@@ -3584,7 +3587,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>168</v>
       </c>
@@ -3606,7 +3609,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>169</v>
       </c>
@@ -3628,7 +3631,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>170</v>
       </c>
@@ -3650,7 +3653,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>171</v>
       </c>
@@ -3672,7 +3675,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>172</v>
       </c>
@@ -3694,7 +3697,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>173</v>
       </c>
@@ -3716,7 +3719,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>174</v>
       </c>
@@ -3738,7 +3741,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>175</v>
       </c>
@@ -3760,7 +3763,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>176</v>
       </c>
@@ -3782,7 +3785,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>177</v>
       </c>
@@ -3804,7 +3807,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>178</v>
       </c>
@@ -3826,7 +3829,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>179</v>
       </c>
@@ -3848,7 +3851,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>180</v>
       </c>
@@ -3870,7 +3873,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>181</v>
       </c>
@@ -3892,7 +3895,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>182</v>
       </c>
@@ -3914,7 +3917,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>183</v>
       </c>
@@ -3936,7 +3939,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>184</v>
       </c>
@@ -3958,7 +3961,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>185</v>
       </c>
@@ -3980,7 +3983,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>186</v>
       </c>
@@ -4002,7 +4005,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>187</v>
       </c>
@@ -4024,7 +4027,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>188</v>
       </c>
@@ -4046,7 +4049,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>189</v>
       </c>
@@ -4068,7 +4071,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>190</v>
       </c>
@@ -4090,7 +4093,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>191</v>
       </c>
@@ -4112,7 +4115,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>192</v>
       </c>
@@ -4134,7 +4137,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>193</v>
       </c>
@@ -4156,7 +4159,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>194</v>
       </c>
@@ -4178,7 +4181,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>195</v>
       </c>
@@ -4200,7 +4203,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>196</v>
       </c>
@@ -4222,7 +4225,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>197</v>
       </c>
@@ -4244,7 +4247,7 @@
         <v>372000</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>198</v>
       </c>
@@ -4266,7 +4269,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>199</v>
       </c>
@@ -4288,7 +4291,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>200</v>
       </c>
@@ -4310,7 +4313,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>201</v>
       </c>
@@ -4332,7 +4335,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>202</v>
       </c>
@@ -4354,7 +4357,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>203</v>
       </c>
@@ -4376,7 +4379,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>204</v>
       </c>
@@ -4398,7 +4401,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>205</v>
       </c>
@@ -4420,7 +4423,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>206</v>
       </c>
@@ -4442,7 +4445,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>207</v>
       </c>
@@ -4464,7 +4467,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>208</v>
       </c>
@@ -4486,7 +4489,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>209</v>
       </c>
@@ -4508,7 +4511,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>210</v>
       </c>
@@ -4530,7 +4533,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>211</v>
       </c>
@@ -4552,7 +4555,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>212</v>
       </c>
@@ -4574,7 +4577,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>213</v>
       </c>
@@ -4596,7 +4599,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>214</v>
       </c>
@@ -4618,7 +4621,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>215</v>
       </c>
@@ -4640,7 +4643,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>216</v>
       </c>
@@ -4662,7 +4665,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>217</v>
       </c>
@@ -4684,7 +4687,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>218</v>
       </c>
@@ -4706,7 +4709,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>219</v>
       </c>
@@ -4728,7 +4731,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>220</v>
       </c>
@@ -4750,7 +4753,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>221</v>
       </c>
@@ -4772,7 +4775,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>222</v>
       </c>
@@ -4794,7 +4797,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>223</v>
       </c>
@@ -4816,7 +4819,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>224</v>
       </c>
@@ -4838,7 +4841,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>225</v>
       </c>
@@ -4860,7 +4863,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>226</v>
       </c>
@@ -4882,7 +4885,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>227</v>
       </c>
@@ -4904,7 +4907,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>228</v>
       </c>
@@ -4926,7 +4929,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>229</v>
       </c>
@@ -4948,7 +4951,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>230</v>
       </c>
@@ -4970,7 +4973,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>231</v>
       </c>
@@ -4992,7 +4995,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>232</v>
       </c>
@@ -5014,7 +5017,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>233</v>
       </c>
@@ -5036,7 +5039,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>234</v>
       </c>
@@ -5058,7 +5061,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>235</v>
       </c>
@@ -5080,7 +5083,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>236</v>
       </c>
@@ -5102,7 +5105,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>237</v>
       </c>
@@ -5124,7 +5127,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>238</v>
       </c>
@@ -5146,7 +5149,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>239</v>
       </c>
@@ -5168,7 +5171,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>240</v>
       </c>
@@ -5190,7 +5193,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>241</v>
       </c>
@@ -5212,7 +5215,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>242</v>
       </c>
@@ -5234,7 +5237,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>243</v>
       </c>
@@ -5256,7 +5259,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>244</v>
       </c>
@@ -5278,7 +5281,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>245</v>
       </c>
@@ -5300,7 +5303,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>246</v>
       </c>
@@ -5322,7 +5325,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>247</v>
       </c>
@@ -5344,7 +5347,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>248</v>
       </c>
@@ -5366,7 +5369,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>249</v>
       </c>
@@ -5388,7 +5391,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>250</v>
       </c>
@@ -5410,7 +5413,7 @@
         <v>186000</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>251</v>
       </c>
@@ -5432,7 +5435,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>252</v>
       </c>
@@ -5454,7 +5457,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>253</v>
       </c>
@@ -5476,7 +5479,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>254</v>
       </c>
@@ -5498,7 +5501,7 @@
         <v>248000</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>255</v>
       </c>
@@ -5521,6 +5524,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A8:F151" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5528,7 +5532,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -5537,12 +5541,12 @@
     <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>257</v>
       </c>
@@ -5550,7 +5554,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -5558,7 +5562,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -5566,7 +5570,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -5574,7 +5578,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>262</v>
       </c>
@@ -5591,7 +5595,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>267</v>
       </c>
@@ -5610,7 +5614,7 @@
         <v>Bắc</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>2</v>
       </c>
@@ -5629,7 +5633,7 @@
         <v>Trung</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>272</v>
       </c>
@@ -5648,7 +5652,7 @@
         <v>Cà phê rang xay 500g</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>275</v>
       </c>
@@ -5667,7 +5671,7 @@
         <v>Mì ăn liền tôm chua cay (thùng 30 gói)</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>278</v>
       </c>
@@ -5680,19 +5684,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>280</v>
       </c>
@@ -5703,7 +5707,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>20</v>
       </c>
@@ -5714,7 +5718,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>21</v>
       </c>
@@ -5725,7 +5729,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>22</v>
       </c>
@@ -5736,7 +5740,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>23</v>
       </c>
@@ -5747,7 +5751,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>23</v>
       </c>
@@ -5758,7 +5762,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>24</v>
       </c>
